--- a/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_01_workbook.xlsx
+++ b/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_01_workbook.xlsx
@@ -286,8 +286,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TSHAPFeatureImportanc" displayName="TSHAPFeatureImportanc" ref="A1:B39" headerRowCount="1">
-  <autoFilter ref="A1:B39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TSHAPFeatureImportanc" displayName="TSHAPFeatureImportanc" ref="A1:B57" headerRowCount="1">
+  <autoFilter ref="A1:B57"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Feature"/>
     <tableColumn id="2" name="Mean |SHAP|"/>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>740368.375</v>
+        <v>742500.375</v>
       </c>
     </row>
     <row r="4">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43536212</v>
+        <v>43534076</v>
       </c>
     </row>
     <row r="5">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1810661.25</v>
+        <v>481625</v>
       </c>
     </row>
     <row r="6">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.0196078431372549</v>
       </c>
     </row>
     <row r="7">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>740368.375*Assumptions!$B$3</f>
+        <f>742500.375*Assumptions!$B$3</f>
         <v/>
       </c>
     </row>
@@ -814,28 +814,28 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>XGBoost does not yet meet the deployment-readiness bar</t>
+          <t>XGBoost meets the deployment-readiness bar</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Holdout ROC-AUC 0.5352 with a 95% bootstrap CI of [0.4731, 0.5992]; deployment checks 2/3 PASS.</t>
+          <t>Holdout ROC-AUC 0.5695 with a 95% bootstrap CI of [0.5083, 0.6296]; deployment checks 3/3 PASS.</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Calibration gap 0.0749 vs. &lt;0.1 threshold; split-half PSI 0.0258 vs. &lt;0.1 threshold.</t>
+          <t>Calibration gap 0.0630 vs. &lt;0.1 threshold; split-half PSI 0.0268 vs. &lt;0.1 threshold.</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Investigate the failing check(s) above before promoting to production; re-run this notebook after any fix to confirm.</t>
+          <t>No further tuning required this cycle.</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>$1,810,661 of real holdout exposure is on applications the model flags as high-risk but that did not default (false positives).</t>
+          <t>$481,625 of real holdout exposure is on applications the model flags as high-risk but that did not default (false positives).</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>False-alarm exposure is 2.45x the real captured exposure — track this ratio on every run.</t>
+          <t>False-alarm exposure is 0.65x the real captured exposure — track this ratio on every run.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.518785155294693</v>
+        <v>0.5169051112741502</v>
       </c>
       <c r="C2" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.553191489361702</v>
+        <v>0.5425379065786256</v>
       </c>
       <c r="C3" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5462062851552947</v>
+        <v>0.5269931523599902</v>
       </c>
       <c r="C4" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5598862802641232</v>
+        <v>0.5802304964539008</v>
       </c>
       <c r="C5" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5302671802396673</v>
+        <v>0.553967962827097</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0221738056229308</v>
+        <v>0.009890891129490527</v>
       </c>
     </row>
     <row r="3">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5364331132306187</v>
+        <v>0.5570555147957936</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0253005409244332</v>
+        <v>0.01414884615922577</v>
       </c>
     </row>
   </sheetData>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5067559305453656</v>
+        <v>0.5364392271949132</v>
       </c>
     </row>
     <row r="3">
@@ -1219,7 +1219,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5526259476644657</v>
+        <v>0.5499663731963805</v>
       </c>
     </row>
     <row r="4">
@@ -1232,7 +1232,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5612007825874297</v>
+        <v>0.5584189288334557</v>
       </c>
     </row>
     <row r="5">
@@ -1245,7 +1245,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.517012105649303</v>
+        <v>0.5628362680361947</v>
       </c>
     </row>
     <row r="6">
@@ -1258,7 +1258,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5137411347517731</v>
+        <v>0.5621790168745415</v>
       </c>
     </row>
     <row r="7">
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.539939471753485</v>
+        <v>0.5515865737344094</v>
       </c>
     </row>
     <row r="8">
@@ -1284,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5372034727317192</v>
+        <v>0.5434550012227928</v>
       </c>
     </row>
     <row r="9">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5775097823428711</v>
+        <v>0.5831499144044998</v>
       </c>
     </row>
     <row r="10">
@@ -1310,7 +1310,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5291177549523111</v>
+        <v>0.5598862802641232</v>
       </c>
     </row>
     <row r="11">
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4983950843727072</v>
+        <v>0.5471998043531425</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5351602488384911</v>
+        <v>0.5694739743286874</v>
       </c>
     </row>
     <row r="3">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.375</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.0196078431372549</v>
       </c>
     </row>
     <row r="5">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.0380952380952381</v>
       </c>
     </row>
     <row r="6">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1468992829322815</v>
+        <v>0.1456471383571625</v>
       </c>
     </row>
   </sheetData>
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03162645921111107</v>
+        <v>0.0261887963861227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="D2" t="n">
         <v>60</v>
@@ -1485,10 +1485,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05439608916640282</v>
+        <v>0.05237876996397972</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D3" t="n">
         <v>60</v>
@@ -1499,10 +1499,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.07365933805704117</v>
+        <v>0.07064177095890045</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="D4" t="n">
         <v>60</v>
@@ -1513,10 +1513,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0913764163851738</v>
+        <v>0.09284714609384537</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2166666666666667</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="D5" t="n">
         <v>60</v>
@@ -1527,10 +1527,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1125684976577759</v>
+        <v>0.1128306686878204</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.15</v>
       </c>
       <c r="D6" t="n">
         <v>60</v>
@@ -1541,10 +1541,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1368248760700226</v>
+        <v>0.1343276649713516</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="D7" t="n">
         <v>60</v>
@@ -1555,10 +1555,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1627648621797562</v>
+        <v>0.1617356240749359</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D8" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1982726752758026</v>
+        <v>0.1929810792207718</v>
       </c>
       <c r="C9" t="n">
         <v>0.2</v>
@@ -1583,10 +1583,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2390360683202744</v>
+        <v>0.2410222440958023</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="D10" t="n">
         <v>60</v>
@@ -1597,10 +1597,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3723455667495728</v>
+        <v>0.3581972718238831</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2166666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
@@ -1632,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2443435192108154</v>
+        <v>0.2490107715129852</v>
       </c>
     </row>
     <row r="3">
@@ -1668,371 +1668,551 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1627954840660095</v>
+        <v>0.1594096273183823</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DAYS_LAST_PHONE_CHANGE</t>
+          <t>YEARS_EMPLOYED</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1283223181962967</v>
+        <v>0.1273747831583023</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_TOTAL</t>
+          <t>INSTAL_PCT_LATE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1209831461310387</v>
+        <v>0.1252078413963318</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>YEARS_EMPLOYED</t>
+          <t>BUREAU_DEBT_TO_CREDIT_RATIO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.120054729282856</v>
+        <v>0.1065347194671631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUREAU_DEBT_TO_CREDIT_RATIO</t>
+          <t>DAYS_LAST_PHONE_CHANGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.113754004240036</v>
+        <v>0.102941632270813</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUREAU_DAYS_CREDIT_MIN</t>
+          <t>PREVAPP_DAYS_SINCE_LAST_DECISION</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.106532134115696</v>
+        <v>0.09776189178228378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANNUITY_TO_CREDIT_RATIO</t>
+          <t>AMT_ANNUITY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1064896658062935</v>
+        <v>0.09567179530858994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMT_INCOME_TOTAL</t>
+          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09957486391067505</v>
+        <v>0.09156161546707153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMT_ANNUITY</t>
+          <t>ANNUITY_TO_CREDIT_RATIO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0991835743188858</v>
+        <v>0.08901356160640717</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL</t>
+          <t>BUREAU_AMT_CREDIT_SUM_TOTAL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09327971935272217</v>
+        <v>0.08574555069208145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CREDIT_TO_INCOME_RATIO</t>
+          <t>ANNUITY_TO_INCOME_RATIO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09141476452350616</v>
+        <v>0.08366869390010834</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANNUITY_TO_INCOME_RATIO</t>
+          <t>AMT_INCOME_TOTAL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08998745679855347</v>
+        <v>0.08332682400941849</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REGION_POPULATION_RELATIVE</t>
+          <t>INSTAL_CNT_PAYMENTS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08102691918611526</v>
+        <v>0.0824175700545311</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_1</t>
+          <t>PREVAPP_MEAN_AMT_APPLICATION</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07753194123506546</v>
+        <v>0.07712895423173904</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMT_REQ_CREDIT_BUREAU_YEAR</t>
+          <t>CREDIT_TO_INCOME_RATIO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07212767004966736</v>
+        <v>0.07389456033706665</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CNT_CHILDREN</t>
+          <t>REGION_POPULATION_RELATIVE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06717890501022339</v>
+        <v>0.07228381931781769</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NAME_HOUSING_TYPE</t>
+          <t>INSTAL_MEAN_PAYMENT_RATIO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06470265984535217</v>
+        <v>0.07034736126661301</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMT_GOODS_PRICE</t>
+          <t>AMT_REQ_CREDIT_BUREAU_YEAR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06152321398258209</v>
+        <v>0.06832945346832275</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_CREDITS</t>
+          <t>PREVAPP_MEAN_AMT_CREDIT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.05697166547179222</v>
+        <v>0.05765805020928383</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMT_CREDIT</t>
+          <t>EXT_SOURCE_1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05211605504155159</v>
+        <v>0.05659428983926773</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CNT_FAM_MEMBERS</t>
+          <t>PREVAPP_MEAN_AMT_ANNUITY</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04742985591292381</v>
+        <v>0.05245864763855934</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3</t>
+          <t>NAME_HOUSING_TYPE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0444539338350296</v>
+        <v>0.05092448741197586</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OCCUPATION_TYPE</t>
+          <t>CNT_FAM_MEMBERS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04097245633602142</v>
+        <v>0.05025336146354675</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REGION_RATING_CLIENT</t>
+          <t>BUREAU_CNT_CREDITS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.04080555960536003</v>
+        <v>0.04737041518092155</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL</t>
+          <t>CNT_CHILDREN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0345955453813076</v>
+        <v>0.04483922198414803</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAME_FAMILY_STATUS</t>
+          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03411054611206055</v>
+        <v>0.0433274433016777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NAME_INCOME_TYPE</t>
+          <t>AMT_GOODS_PRICE</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.03328007087111473</v>
+        <v>0.04250170290470123</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FLAG_OWN_CAR</t>
+          <t>CC_CNT_RECORDS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.03300398588180542</v>
+        <v>0.04248650372028351</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CODE_GENDER</t>
+          <t>POS_MEAN_SK_DPD_DEF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.03010246530175209</v>
+        <v>0.04159046337008476</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NAME_EDUCATION_TYPE</t>
+          <t>AMT_CREDIT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.02820884622633457</v>
+        <v>0.03813035786151886</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_ACTIVE</t>
+          <t>POS_CNT_RECORDS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.02513437718153</v>
+        <v>0.03455501422286034</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OBS_30_CNT_SOCIAL_CIRCLE</t>
+          <t>POS_CNT_COMPLETED</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02208095602691174</v>
+        <v>0.03455351293087006</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BUREAU_MAX_DAYS_OVERDUE</t>
+          <t>EXT_SOURCE_3</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01366411987692118</v>
+        <v>0.03421628475189209</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FLAG_OWN_REALTY</t>
+          <t>BUREAU_TOTAL_DPD_MONTHS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01136209070682526</v>
+        <v>0.03014647215604782</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_PROLONGED</t>
+          <t>REGION_RATING_CLIENT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.005085442215204239</v>
+        <v>0.02926610969007015</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NAME_CONTRACT_TYPE</t>
+          <t>CODE_GENDER</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.004650071263313293</v>
+        <v>0.02903167344629765</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>CC_MEAN_UTILIZATION</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.02823884971439838</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NAME_INCOME_TYPE</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0237161610275507</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NAME_FAMILY_STATUS</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0233148131519556</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CC_MEAN_BALANCE</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.02258514799177647</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PREVAPP_APPROVAL_RATE</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.02248682454228401</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OCCUPATION_TYPE</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.02181568555533886</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NAME_EDUCATION_TYPE</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.02179643511772156</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FLAG_OWN_CAR</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.01914237625896931</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PREVAPP_REFUSAL_RATE</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.01648606546223164</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BUREAU_CNT_ACTIVE</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.01637214608490467</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PREVAPP_CNT_APPROVED</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.01573453657329082</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OBS_30_CNT_SOCIAL_CIRCLE</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.01460946444422007</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BUREAU_MAX_DAYS_OVERDUE</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.01444574166089296</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PREVAPP_CNT_TOTAL</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.007965506054461002</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FLAG_OWN_REALTY</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.006850252859294415</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CC_SUM_SK_DPD</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.006551195401698351</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>DEF_30_CNT_SOCIAL_CIRCLE</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0.003677503205835819</v>
+      <c r="B55" t="n">
+        <v>0.00332100223749876</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PREVAPP_CNT_REFUSED</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.002424334641546011</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NAME_CONTRACT_TYPE</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.00228417944163084</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B39">
+  <conditionalFormatting sqref="B2:B57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2090,11 +2270,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGE_YEARS &gt; 57.80</t>
+          <t>EXT_SOURCE_2 &lt;= 0.24</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.04028606419673005</v>
+        <v>0.0449001390489317</v>
       </c>
     </row>
     <row r="3">
@@ -2105,11 +2285,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DAYS_LAST_PHONE_CHANGE &lt;= -3040.50</t>
+          <t>AGE_YEARS &gt; 57.80</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03409462644973454</v>
+        <v>0.04074965037846207</v>
       </c>
     </row>
     <row r="4">
@@ -2120,11 +2300,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.24 &lt; EXT_SOURCE_2 &lt;= 0.49</t>
+          <t>DAYS_LAST_PHONE_CHANGE &lt;= -3040.50</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03377905816615062</v>
+        <v>0.03231998132830564</v>
       </c>
     </row>
     <row r="5">
@@ -2135,11 +2315,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3 &lt;= 0.49</t>
+          <t>INSTAL_PCT_LATE &lt;= 0.00</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02739917275555684</v>
+        <v>0.0274794658262722</v>
       </c>
     </row>
     <row r="6">
@@ -2150,11 +2330,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL &lt;= 0.00</t>
+          <t>REGION_POPULATION_RELATIVE &lt;= 0.02</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02245755387214465</v>
+        <v>0.02496083532802462</v>
       </c>
     </row>
     <row r="7">
@@ -2165,11 +2345,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CNT_CHILDREN &gt; 1.00</t>
+          <t>POS_MEAN_SK_DPD_DEF &gt; 0.00</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02182567921374433</v>
+        <v>0.02294615382064003</v>
       </c>
     </row>
     <row r="8">
@@ -2180,11 +2360,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OCCUPATION_TYPE=4</t>
+          <t>PREVAPP_MEAN_AMT_APPLICATION &gt; 150011.81</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.01841431241744346</v>
+        <v>-0.01976760101845814</v>
       </c>
     </row>
     <row r="9">
@@ -2195,11 +2375,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.09 &lt; BUREAU_DEBT_TO_CREDIT_RATIO &lt;= 0.27</t>
+          <t>BUREAU_DEBT_TO_CREDIT_RATIO &lt;= 0.02</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01432598769641063</v>
+        <v>0.01782011547027264</v>
       </c>
     </row>
     <row r="10">
@@ -2210,11 +2390,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BUREAU_DEBT_TO_CREDIT_RATIO &gt; 0.27</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.05736707727262246</v>
+        <v>-0.02472622748150122</v>
       </c>
     </row>
     <row r="11">
@@ -2225,11 +2405,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGE_YEARS &lt;= 32.24</t>
+          <t>0.49 &lt; EXT_SOURCE_2 &lt;= 0.75</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.03839345811820714</v>
+        <v>-0.02428055894240437</v>
       </c>
     </row>
     <row r="12">
@@ -2240,11 +2420,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.49 &lt; EXT_SOURCE_2 &lt;= 0.75</t>
+          <t>INSTAL_CNT_PAYMENTS &gt; 32.00</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.03215635530686162</v>
+        <v>-0.02267925224931631</v>
       </c>
     </row>
     <row r="13">
@@ -2255,11 +2435,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DAYS_LAST_PHONE_CHANGE &lt;= -3040.50</t>
+          <t>AMT_REQ_CREDIT_BUREAU_YEAR &gt; 7.00</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02942529502755888</v>
+        <v>-0.01873152705534917</v>
       </c>
     </row>
     <row r="14">
@@ -2270,11 +2450,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3 &lt;= 0.49</t>
+          <t>EXT_SOURCE_3 &gt; 0.49</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02534396953665574</v>
+        <v>-0.01835392637849322</v>
       </c>
     </row>
     <row r="15">
@@ -2285,11 +2465,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL &gt; 46309.19</t>
+          <t>-3040.50 &lt; DAYS_LAST_PHONE_CHANGE &lt;= -2036.00</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.02482044548488171</v>
+        <v>-0.0180392848340356</v>
       </c>
     </row>
     <row r="16">
@@ -2300,11 +2480,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_CREDITS &gt; 3.00</t>
+          <t>94563.57 &lt; PREVAPP_MEAN_AMT_APPLICATION &lt;= 150011.81</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01695631264180643</v>
+        <v>-0.01656455797825201</v>
       </c>
     </row>
     <row r="17">
@@ -2315,11 +2495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL &lt;= 0.00</t>
+          <t>BUREAU_DEBT_TO_CREDIT_RATIO &lt;= 0.02</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01676722103857558</v>
+        <v>0.01578721506607648</v>
       </c>
     </row>
     <row r="18">
@@ -2330,11 +2510,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_2 &gt; 0.75</t>
+          <t>INSTAL_PCT_LATE &gt; 0.37</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.04730528999761621</v>
+        <v>-0.04773020996082463</v>
       </c>
     </row>
     <row r="19">
@@ -2345,11 +2525,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAYS_LAST_PHONE_CHANGE &lt;= -3040.50</t>
+          <t>AGE_YEARS &gt; 57.80</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03487032809563374</v>
+        <v>0.039440608067128</v>
       </c>
     </row>
     <row r="20">
@@ -2360,11 +2540,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REGION_POPULATION_RELATIVE &lt;= 0.02</t>
+          <t>0.24 &lt; EXT_SOURCE_2 &lt;= 0.49</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0268421058172795</v>
+        <v>0.0278341690464174</v>
       </c>
     </row>
     <row r="21">
@@ -2375,11 +2555,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3 &lt;= 0.49</t>
+          <t>POS_MEAN_SK_DPD_DEF &gt; 0.00</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02585573414076881</v>
+        <v>0.02763277833844535</v>
       </c>
     </row>
     <row r="22">
@@ -2390,11 +2570,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMT_ANNUITY &lt;= 12237.39</t>
+          <t>EXT_SOURCE_3 &lt;= 0.49</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.01920862138270822</v>
+        <v>0.02479248671426128</v>
       </c>
     </row>
     <row r="23">
@@ -2405,11 +2585,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL &lt;= 0.00</t>
+          <t>INSTAL_CNT_PAYMENTS &gt; 32.00</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0181933158345824</v>
+        <v>-0.02069156372094281</v>
       </c>
     </row>
     <row r="24">
@@ -2420,11 +2600,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>153215.47 &lt; BUREAU_AMT_CREDIT_SUM_TOTAL &lt;= 309332.65</t>
+          <t>0.09 &lt; BUREAU_DEBT_TO_CREDIT_RATIO &lt;= 0.27</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.01762297027922084</v>
+        <v>0.01955658717621375</v>
       </c>
     </row>
     <row r="25">
@@ -2435,11 +2615,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAME_HOUSING_TYPE=0</t>
+          <t>94563.57 &lt; PREVAPP_MEAN_AMT_APPLICATION &lt;= 150011.81</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.0172657324137706</v>
+        <v>-0.01617629456514239</v>
       </c>
     </row>
   </sheetData>
